--- a/db/A7XLK-1403-FinancialWebsite.xlsx
+++ b/db/A7XLK-1403-FinancialWebsite.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10509"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou/db/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{310F0A7E-6139-FA47-AF19-01AB9E15E7B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE2523CB-4212-1042-889D-D23620D05BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="6980" windowWidth="39960" windowHeight="16060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1940" windowWidth="27980" windowHeight="16060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transformed by JSON-CSV.CO" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
   <si>
     <t>https://www.taishinbank.com.tw/TSB/personal/</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -304,62 +304,79 @@
     <t>fig/XLK-1401-News/INV-3011-Bank-元大投信.jpg</t>
   </si>
   <si>
+    <t>fig/XLK-1401-News/INV-3012-Stock-鉅亨基金.png</t>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/INV-3012-Stock-理財網.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/INV-3012-Stock-yahoo.png</t>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/INV-3012-Stock-台灣股市資訊網.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/INV-3012-Stock-CMoney.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/INV-3012-Stock-Morningstar.png</t>
+  </si>
+  <si>
+    <t>https://www.fXLK-1401-News/INViz.com/</t>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/INV-3012-Stock-Dividendcom.png</t>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/INV-3012-Stock-Jitta.png</t>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/INV-3012-Stock-ETFcom.png</t>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/INV-3012-Stock-ETFdb.png</t>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/INV-3013-Magazine-商業週刊.png</t>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/INV-3013-Magazine-今周刊.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/INV-3013-Magazine-理財週刊.jpg</t>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/INV-3013-Magazine-退休基金.png</t>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/INV-3013-Magazine-Money錢.png</t>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/INV-3012-Stock-Finviz.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FINViz.com</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>212</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TradingView</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>fig/XLK-1401-News/INV-3011-Bank-元大證劵.jpg</t>
-  </si>
-  <si>
-    <t>fig/XLK-1401-News/INV-3012-Stock-鉅亨基金.png</t>
-  </si>
-  <si>
-    <t>fig/XLK-1401-News/INV-3012-Stock-理財網.jpeg</t>
-  </si>
-  <si>
-    <t>fig/XLK-1401-News/INV-3012-Stock-yahoo.png</t>
-  </si>
-  <si>
-    <t>fig/XLK-1401-News/INV-3012-Stock-台灣股市資訊網.jpeg</t>
-  </si>
-  <si>
-    <t>fig/XLK-1401-News/INV-3012-Stock-CMoney.jpeg</t>
-  </si>
-  <si>
-    <t>fig/XLK-1401-News/INV-3012-Stock-Morningstar.png</t>
-  </si>
-  <si>
-    <t>https://www.fXLK-1401-News/INViz.com/</t>
-  </si>
-  <si>
-    <t>fig/XLK-1401-News/INV-3012-Stock-Dividendcom.png</t>
-  </si>
-  <si>
-    <t>fig/XLK-1401-News/INV-3012-Stock-Jitta.png</t>
-  </si>
-  <si>
-    <t>fig/XLK-1401-News/INV-3012-Stock-ETFcom.png</t>
-  </si>
-  <si>
-    <t>fig/XLK-1401-News/INV-3012-Stock-ETFdb.png</t>
-  </si>
-  <si>
-    <t>fig/XLK-1401-News/INV-3013-Magazine-商業週刊.png</t>
-  </si>
-  <si>
-    <t>fig/XLK-1401-News/INV-3013-Magazine-今周刊.jpeg</t>
-  </si>
-  <si>
-    <t>fig/XLK-1401-News/INV-3013-Magazine-理財週刊.jpg</t>
-  </si>
-  <si>
-    <t>fig/XLK-1401-News/INV-3013-Magazine-退休基金.png</t>
-  </si>
-  <si>
-    <t>fig/XLK-1401-News/INV-3013-Magazine-Money錢.png</t>
-  </si>
-  <si>
-    <t>fig/XLK-1401-News/INV-3012-Stock-Finviz.png</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>FINViz.com</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/INV-3012-Stock-TradingView.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tw.tradingview.com/</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -741,7 +758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="2"/>
@@ -826,7 +843,7 @@
         <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>57</v>
@@ -837,16 +854,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" t="s">
-        <v>6</v>
+        <v>90</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="E6" t="s">
         <v>23</v>
@@ -854,16 +871,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>17</v>
+        <v>69</v>
+      </c>
+      <c r="D7" t="s">
+        <v>6</v>
       </c>
       <c r="E7" t="s">
         <v>23</v>
@@ -871,16 +888,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="E8" t="s">
         <v>23</v>
@@ -888,16 +905,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E9" t="s">
         <v>23</v>
@@ -905,16 +922,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>55</v>
+        <v>47</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="E10" t="s">
         <v>23</v>
@@ -922,16 +939,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" t="s">
-        <v>22</v>
+        <v>54</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
         <v>23</v>
@@ -939,16 +956,16 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s">
         <v>23</v>
@@ -956,16 +973,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="E13" t="s">
         <v>23</v>
@@ -973,16 +990,16 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E14" t="s">
         <v>23</v>
@@ -990,16 +1007,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E15" t="s">
         <v>23</v>
@@ -1007,16 +1024,16 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" t="s">
-        <v>32</v>
+        <v>78</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="E16" t="s">
         <v>23</v>
@@ -1024,33 +1041,33 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>37</v>
+        <v>53</v>
+      </c>
+      <c r="B17" t="s">
+        <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>81</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>44</v>
+        <v>79</v>
+      </c>
+      <c r="D17" t="s">
+        <v>32</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E18" t="s">
         <v>43</v>
@@ -1058,16 +1075,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E19" t="s">
         <v>43</v>
@@ -1075,67 +1092,85 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B20" t="s">
-        <v>61</v>
+        <v>42</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>84</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>62</v>
+        <v>82</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="E20" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="6" t="s">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B22" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D21" s="7" t="s">
+      <c r="C22" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E22" s="4" t="s">
         <v>43</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E20">
-    <sortCondition ref="A2:A20"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E21">
+    <sortCondition ref="A2:A21"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E22:E1048576 E1:E20" xr:uid="{B6A4967F-A3DD-9142-986A-3AC4BF5BDC9F}">
-      <formula1>$E$2:$E$19</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E23:E1048576 E1:E21" xr:uid="{B6A4967F-A3DD-9142-986A-3AC4BF5BDC9F}">
+      <formula1>$E$2:$E$20</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21" xr:uid="{F7BF2D6E-5633-A140-B778-86A6E9245256}">
-      <formula1>$E$2:$E$20</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E22" xr:uid="{F7BF2D6E-5633-A140-B778-86A6E9245256}">
+      <formula1>$E$2:$E$21</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{5223C5F8-8371-9A46-B6A0-BA0E916D8371}"/>
     <hyperlink ref="D3" r:id="rId2" xr:uid="{9A0A6CEF-14EC-4B4C-886C-C517B07F8A6E}"/>
-    <hyperlink ref="D7" r:id="rId3" xr:uid="{A7A4679C-8163-A249-8515-842528737D9B}"/>
+    <hyperlink ref="D8" r:id="rId3" xr:uid="{A7A4679C-8163-A249-8515-842528737D9B}"/>
     <hyperlink ref="D4" r:id="rId4" xr:uid="{38C14951-FFF9-6649-B00B-F823E1470E38}"/>
-    <hyperlink ref="D11" r:id="rId5" xr:uid="{D19A8699-FAEF-5C48-9EC4-BC94B493346F}"/>
-    <hyperlink ref="D9" r:id="rId6" xr:uid="{82AF1437-B497-E54D-8F1C-9012604D7DF8}"/>
-    <hyperlink ref="D15" r:id="rId7" xr:uid="{623B9E50-F476-FE41-936B-A104D53DE847}"/>
-    <hyperlink ref="D13" r:id="rId8" xr:uid="{B95817E1-7F33-AD44-88EA-9A3396CB465B}"/>
-    <hyperlink ref="D12" r:id="rId9" display="https://www.finviz.com/" xr:uid="{32AB97EA-201A-BE42-A4AF-7F73485D13C1}"/>
-    <hyperlink ref="D8" r:id="rId10" xr:uid="{0B33FA6B-A5F3-9148-BAE5-529D92A11A3A}"/>
-    <hyperlink ref="D14" r:id="rId11" xr:uid="{72177DED-5893-B94C-B83E-17819C8FD397}"/>
-    <hyperlink ref="D10" r:id="rId12" xr:uid="{51F70D59-990A-E64C-AC1B-3DD9C8D60991}"/>
+    <hyperlink ref="D12" r:id="rId5" xr:uid="{D19A8699-FAEF-5C48-9EC4-BC94B493346F}"/>
+    <hyperlink ref="D10" r:id="rId6" xr:uid="{82AF1437-B497-E54D-8F1C-9012604D7DF8}"/>
+    <hyperlink ref="D16" r:id="rId7" xr:uid="{623B9E50-F476-FE41-936B-A104D53DE847}"/>
+    <hyperlink ref="D14" r:id="rId8" xr:uid="{B95817E1-7F33-AD44-88EA-9A3396CB465B}"/>
+    <hyperlink ref="D13" r:id="rId9" display="https://www.finviz.com/" xr:uid="{32AB97EA-201A-BE42-A4AF-7F73485D13C1}"/>
+    <hyperlink ref="D9" r:id="rId10" xr:uid="{0B33FA6B-A5F3-9148-BAE5-529D92A11A3A}"/>
+    <hyperlink ref="D15" r:id="rId11" xr:uid="{72177DED-5893-B94C-B83E-17819C8FD397}"/>
+    <hyperlink ref="D11" r:id="rId12" xr:uid="{51F70D59-990A-E64C-AC1B-3DD9C8D60991}"/>
     <hyperlink ref="D5" r:id="rId13" xr:uid="{F6076A74-88FC-2A4F-9C6A-1F5A096C705E}"/>
-    <hyperlink ref="D20" r:id="rId14" xr:uid="{EE6720B0-AFC0-CA41-B1B7-48FDA8B34FBC}"/>
-    <hyperlink ref="D21" r:id="rId15" xr:uid="{A1D685D6-89C6-FE47-A7B4-5F731490770D}"/>
+    <hyperlink ref="D21" r:id="rId14" xr:uid="{EE6720B0-AFC0-CA41-B1B7-48FDA8B34FBC}"/>
+    <hyperlink ref="D22" r:id="rId15" xr:uid="{A1D685D6-89C6-FE47-A7B4-5F731490770D}"/>
+    <hyperlink ref="D6" r:id="rId16" xr:uid="{6C161D74-776A-2D4A-87DC-71F70BAEA37C}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait"/>
